--- a/artfynd/A 59698-2025 artfynd.xlsx
+++ b/artfynd/A 59698-2025 artfynd.xlsx
@@ -1004,7 +1004,7 @@
         <v>135839090</v>
       </c>
       <c r="B5" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135839103</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135839084</v>
       </c>
       <c r="B7" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135839092</v>
       </c>
       <c r="B8" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>135839082</v>
       </c>
       <c r="B13" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135839083</v>
       </c>
       <c r="B14" t="n">
-        <v>87695</v>
+        <v>87697</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>135839096</v>
       </c>
       <c r="B15" t="n">
-        <v>87695</v>
+        <v>87697</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>135839101</v>
       </c>
       <c r="B16" t="n">
-        <v>87695</v>
+        <v>87697</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>135839081</v>
       </c>
       <c r="B17" t="n">
-        <v>93034</v>
+        <v>93036</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 59698-2025 artfynd.xlsx
+++ b/artfynd/A 59698-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839087</v>
       </c>
       <c r="B2" t="n">
-        <v>83419</v>
+        <v>83421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135839105</v>
       </c>
       <c r="B3" t="n">
-        <v>83419</v>
+        <v>83421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135839098</v>
       </c>
       <c r="B4" t="n">
-        <v>81125</v>
+        <v>81127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135839090</v>
       </c>
       <c r="B5" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135839103</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135839084</v>
       </c>
       <c r="B7" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135839092</v>
       </c>
       <c r="B8" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135839093</v>
       </c>
       <c r="B9" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>135839089</v>
       </c>
       <c r="B10" t="n">
-        <v>83433</v>
+        <v>83435</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>135839094</v>
       </c>
       <c r="B11" t="n">
-        <v>83433</v>
+        <v>83435</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>135839095</v>
       </c>
       <c r="B12" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>135839082</v>
       </c>
       <c r="B13" t="n">
-        <v>92275</v>
+        <v>92289</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135839083</v>
       </c>
       <c r="B14" t="n">
-        <v>87697</v>
+        <v>87699</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>135839096</v>
       </c>
       <c r="B15" t="n">
-        <v>87697</v>
+        <v>87699</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>135839101</v>
       </c>
       <c r="B16" t="n">
-        <v>87697</v>
+        <v>87699</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>135839081</v>
       </c>
       <c r="B17" t="n">
-        <v>93036</v>
+        <v>93051</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>135839099</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>135839104</v>
       </c>
       <c r="B19" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>135839102</v>
       </c>
       <c r="B20" t="n">
-        <v>83426</v>
+        <v>83428</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 59698-2025 artfynd.xlsx
+++ b/artfynd/A 59698-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839087</v>
       </c>
       <c r="B2" t="n">
-        <v>83421</v>
+        <v>83422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135839105</v>
       </c>
       <c r="B3" t="n">
-        <v>83421</v>
+        <v>83422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135839098</v>
       </c>
       <c r="B4" t="n">
-        <v>81127</v>
+        <v>81128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135839090</v>
       </c>
       <c r="B5" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135839103</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135839084</v>
       </c>
       <c r="B7" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135839092</v>
       </c>
       <c r="B8" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135839093</v>
       </c>
       <c r="B9" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>135839089</v>
       </c>
       <c r="B10" t="n">
-        <v>83435</v>
+        <v>83436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>135839094</v>
       </c>
       <c r="B11" t="n">
-        <v>83435</v>
+        <v>83436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>135839095</v>
       </c>
       <c r="B12" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>135839082</v>
       </c>
       <c r="B13" t="n">
-        <v>92289</v>
+        <v>92290</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135839083</v>
       </c>
       <c r="B14" t="n">
-        <v>87699</v>
+        <v>87700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>135839096</v>
       </c>
       <c r="B15" t="n">
-        <v>87699</v>
+        <v>87700</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>135839101</v>
       </c>
       <c r="B16" t="n">
-        <v>87699</v>
+        <v>87700</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>135839081</v>
       </c>
       <c r="B17" t="n">
-        <v>93051</v>
+        <v>93052</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>135839099</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>135839104</v>
       </c>
       <c r="B19" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>135839102</v>
       </c>
       <c r="B20" t="n">
-        <v>83428</v>
+        <v>83429</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 59698-2025 artfynd.xlsx
+++ b/artfynd/A 59698-2025 artfynd.xlsx
@@ -1004,7 +1004,7 @@
         <v>135839090</v>
       </c>
       <c r="B5" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135839103</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135839084</v>
       </c>
       <c r="B7" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135839092</v>
       </c>
       <c r="B8" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>135839082</v>
       </c>
       <c r="B13" t="n">
-        <v>92290</v>
+        <v>92291</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135839083</v>
       </c>
       <c r="B14" t="n">
-        <v>87700</v>
+        <v>87701</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>135839096</v>
       </c>
       <c r="B15" t="n">
-        <v>87700</v>
+        <v>87701</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>135839101</v>
       </c>
       <c r="B16" t="n">
-        <v>87700</v>
+        <v>87701</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>135839081</v>
       </c>
       <c r="B17" t="n">
-        <v>93052</v>
+        <v>93053</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 59698-2025 artfynd.xlsx
+++ b/artfynd/A 59698-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839087</v>
       </c>
       <c r="B2" t="n">
-        <v>83422</v>
+        <v>83423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135839105</v>
       </c>
       <c r="B3" t="n">
-        <v>83422</v>
+        <v>83423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135839098</v>
       </c>
       <c r="B4" t="n">
-        <v>81128</v>
+        <v>81129</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135839090</v>
       </c>
       <c r="B5" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135839103</v>
       </c>
       <c r="B6" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135839084</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135839092</v>
       </c>
       <c r="B8" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135839093</v>
       </c>
       <c r="B9" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>135839089</v>
       </c>
       <c r="B10" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>135839094</v>
       </c>
       <c r="B11" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>135839095</v>
       </c>
       <c r="B12" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>135839082</v>
       </c>
       <c r="B13" t="n">
-        <v>92291</v>
+        <v>92292</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135839083</v>
       </c>
       <c r="B14" t="n">
-        <v>87701</v>
+        <v>87702</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>135839096</v>
       </c>
       <c r="B15" t="n">
-        <v>87701</v>
+        <v>87702</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>135839101</v>
       </c>
       <c r="B16" t="n">
-        <v>87701</v>
+        <v>87702</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>135839081</v>
       </c>
       <c r="B17" t="n">
-        <v>93053</v>
+        <v>93054</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>135839099</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>135839104</v>
       </c>
       <c r="B19" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>135839102</v>
       </c>
       <c r="B20" t="n">
-        <v>83429</v>
+        <v>83430</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 59698-2025 artfynd.xlsx
+++ b/artfynd/A 59698-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839087</v>
       </c>
       <c r="B2" t="n">
-        <v>83423</v>
+        <v>83427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135839105</v>
       </c>
       <c r="B3" t="n">
-        <v>83423</v>
+        <v>83427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135839098</v>
       </c>
       <c r="B4" t="n">
-        <v>81129</v>
+        <v>81133</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135839090</v>
       </c>
       <c r="B5" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135839103</v>
       </c>
       <c r="B6" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135839084</v>
       </c>
       <c r="B7" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135839092</v>
       </c>
       <c r="B8" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135839093</v>
       </c>
       <c r="B9" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>135839089</v>
       </c>
       <c r="B10" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>135839094</v>
       </c>
       <c r="B11" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>135839095</v>
       </c>
       <c r="B12" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>135839082</v>
       </c>
       <c r="B13" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135839083</v>
       </c>
       <c r="B14" t="n">
-        <v>87702</v>
+        <v>87708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>135839096</v>
       </c>
       <c r="B15" t="n">
-        <v>87702</v>
+        <v>87708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>135839101</v>
       </c>
       <c r="B16" t="n">
-        <v>87702</v>
+        <v>87708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>135839081</v>
       </c>
       <c r="B17" t="n">
-        <v>93054</v>
+        <v>93060</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>135839099</v>
       </c>
       <c r="B18" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>135839104</v>
       </c>
       <c r="B19" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>135839102</v>
       </c>
       <c r="B20" t="n">
-        <v>83430</v>
+        <v>83434</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 59698-2025 artfynd.xlsx
+++ b/artfynd/A 59698-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839087</v>
       </c>
       <c r="B2" t="n">
-        <v>83427</v>
+        <v>83428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135839105</v>
       </c>
       <c r="B3" t="n">
-        <v>83427</v>
+        <v>83428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135839098</v>
       </c>
       <c r="B4" t="n">
-        <v>81133</v>
+        <v>81134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135839090</v>
       </c>
       <c r="B5" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135839103</v>
       </c>
       <c r="B6" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135839084</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135839092</v>
       </c>
       <c r="B8" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135839093</v>
       </c>
       <c r="B9" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>135839089</v>
       </c>
       <c r="B10" t="n">
-        <v>83441</v>
+        <v>83442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>135839094</v>
       </c>
       <c r="B11" t="n">
-        <v>83441</v>
+        <v>83442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>135839095</v>
       </c>
       <c r="B12" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>135839082</v>
       </c>
       <c r="B13" t="n">
-        <v>92298</v>
+        <v>92299</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135839083</v>
       </c>
       <c r="B14" t="n">
-        <v>87708</v>
+        <v>87709</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>135839096</v>
       </c>
       <c r="B15" t="n">
-        <v>87708</v>
+        <v>87709</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>135839101</v>
       </c>
       <c r="B16" t="n">
-        <v>87708</v>
+        <v>87709</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>135839081</v>
       </c>
       <c r="B17" t="n">
-        <v>93060</v>
+        <v>93061</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>135839099</v>
       </c>
       <c r="B18" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>135839104</v>
       </c>
       <c r="B19" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>135839102</v>
       </c>
       <c r="B20" t="n">
-        <v>83434</v>
+        <v>83435</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 59698-2025 artfynd.xlsx
+++ b/artfynd/A 59698-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839087</v>
       </c>
       <c r="B2" t="n">
-        <v>83428</v>
+        <v>83432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135839105</v>
       </c>
       <c r="B3" t="n">
-        <v>83428</v>
+        <v>83432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135839098</v>
       </c>
       <c r="B4" t="n">
-        <v>81134</v>
+        <v>81138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135839090</v>
       </c>
       <c r="B5" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135839103</v>
       </c>
       <c r="B6" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135839084</v>
       </c>
       <c r="B7" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135839092</v>
       </c>
       <c r="B8" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135839093</v>
       </c>
       <c r="B9" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>135839089</v>
       </c>
       <c r="B10" t="n">
-        <v>83442</v>
+        <v>83446</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>135839094</v>
       </c>
       <c r="B11" t="n">
-        <v>83442</v>
+        <v>83446</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>135839095</v>
       </c>
       <c r="B12" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>135839082</v>
       </c>
       <c r="B13" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135839083</v>
       </c>
       <c r="B14" t="n">
-        <v>87709</v>
+        <v>87715</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>135839096</v>
       </c>
       <c r="B15" t="n">
-        <v>87709</v>
+        <v>87715</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>135839101</v>
       </c>
       <c r="B16" t="n">
-        <v>87709</v>
+        <v>87715</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>135839081</v>
       </c>
       <c r="B17" t="n">
-        <v>93061</v>
+        <v>93067</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>135839099</v>
       </c>
       <c r="B18" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>135839104</v>
       </c>
       <c r="B19" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>135839102</v>
       </c>
       <c r="B20" t="n">
-        <v>83435</v>
+        <v>83439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 59698-2025 artfynd.xlsx
+++ b/artfynd/A 59698-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839087</v>
       </c>
       <c r="B2" t="n">
-        <v>83432</v>
+        <v>83438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135839105</v>
       </c>
       <c r="B3" t="n">
-        <v>83432</v>
+        <v>83438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135839098</v>
       </c>
       <c r="B4" t="n">
-        <v>81138</v>
+        <v>81144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135839090</v>
       </c>
       <c r="B5" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135839103</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135839084</v>
       </c>
       <c r="B7" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135839092</v>
       </c>
       <c r="B8" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135839093</v>
       </c>
       <c r="B9" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>135839089</v>
       </c>
       <c r="B10" t="n">
-        <v>83446</v>
+        <v>83452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>135839094</v>
       </c>
       <c r="B11" t="n">
-        <v>83446</v>
+        <v>83452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>135839095</v>
       </c>
       <c r="B12" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>135839082</v>
       </c>
       <c r="B13" t="n">
-        <v>92305</v>
+        <v>92312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135839083</v>
       </c>
       <c r="B14" t="n">
-        <v>87715</v>
+        <v>87722</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>135839096</v>
       </c>
       <c r="B15" t="n">
-        <v>87715</v>
+        <v>87722</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>135839101</v>
       </c>
       <c r="B16" t="n">
-        <v>87715</v>
+        <v>87722</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>135839081</v>
       </c>
       <c r="B17" t="n">
-        <v>93067</v>
+        <v>93074</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>135839099</v>
       </c>
       <c r="B18" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>135839104</v>
       </c>
       <c r="B19" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>135839102</v>
       </c>
       <c r="B20" t="n">
-        <v>83439</v>
+        <v>83445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 59698-2025 artfynd.xlsx
+++ b/artfynd/A 59698-2025 artfynd.xlsx
@@ -1004,7 +1004,7 @@
         <v>135839090</v>
       </c>
       <c r="B5" t="n">
-        <v>92083</v>
+        <v>92084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135839103</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135839084</v>
       </c>
       <c r="B7" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135839092</v>
       </c>
       <c r="B8" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>135839082</v>
       </c>
       <c r="B13" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>135839081</v>
       </c>
       <c r="B17" t="n">
-        <v>93074</v>
+        <v>93075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 59698-2025 artfynd.xlsx
+++ b/artfynd/A 59698-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839087</v>
       </c>
       <c r="B2" t="n">
-        <v>83438</v>
+        <v>83451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135839105</v>
       </c>
       <c r="B3" t="n">
-        <v>83438</v>
+        <v>83451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135839098</v>
       </c>
       <c r="B4" t="n">
-        <v>81144</v>
+        <v>81157</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135839090</v>
       </c>
       <c r="B5" t="n">
-        <v>92084</v>
+        <v>92097</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135839103</v>
       </c>
       <c r="B6" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135839084</v>
       </c>
       <c r="B7" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135839092</v>
       </c>
       <c r="B8" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>135839093</v>
       </c>
       <c r="B9" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>135839089</v>
       </c>
       <c r="B10" t="n">
-        <v>83452</v>
+        <v>83465</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>135839094</v>
       </c>
       <c r="B11" t="n">
-        <v>83452</v>
+        <v>83465</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>135839095</v>
       </c>
       <c r="B12" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>135839082</v>
       </c>
       <c r="B13" t="n">
-        <v>92313</v>
+        <v>92326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135839083</v>
       </c>
       <c r="B14" t="n">
-        <v>87722</v>
+        <v>87735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>135839096</v>
       </c>
       <c r="B15" t="n">
-        <v>87722</v>
+        <v>87735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>135839101</v>
       </c>
       <c r="B16" t="n">
-        <v>87722</v>
+        <v>87735</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>135839081</v>
       </c>
       <c r="B17" t="n">
-        <v>93075</v>
+        <v>93088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>135839099</v>
       </c>
       <c r="B18" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>135839104</v>
       </c>
       <c r="B19" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>135839102</v>
       </c>
       <c r="B20" t="n">
-        <v>83445</v>
+        <v>83458</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
